--- a/src/datapipeline/outputs/medical_incidents.xlsx
+++ b/src/datapipeline/outputs/medical_incidents.xlsx
@@ -443,24 +443,24 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>**Internal Medicine**</t>
+          <t>**Surgery**</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>A 72-year-old patient with known chronic kidney disease (eGFR 35 mL/min) was admitted to the general medical floor for pneumonia. A new resident, unfamiliar with the patient's full medical history and under pressure from a heavy patient load during a weekend shift, prescribed a standard dose of Vancomycin. This dosage typically requires renal adjustment in patients with impaired kidney function. The electronic prescribing system did issue a low-level warning about potential renal toxicity, but the resident, focused on managing multiple tasks, overrode it without a detailed review of the patient's most recent renal function labs. The evening nurse administered the first dose. The next morning, during a routine medication reconciliation, a more experienced clinical pharmacist reviewing the patient's profile noted the discrepancy and immediately flagged it. Subsequent lab tests showed a slight but noticeable increase in creatinine and a higher-than-expected trough Vancomycin level, indicating a potential for acute kidney injury if the full course had been administered without adjustment. The incident highlighted a systemic issue where the EHR's warning system allowed easy override of significant alerts without mandatory secondary review for high-risk medications, especially during high-stress periods with less experienced staff.</t>
+          <t>A 72-year-old male underwent elective knee replacement surgery. During the procedure, the surgical team relied on a hand-written white board for patient information and surgical site verification, as the electronic system was temporarily down. The pre-operative checklist was completed verbally but the consent form in the paper chart was for the left knee, while the patient's intended surgery was for the right knee, as indicated by a faint marker on the wrong leg. The surgeon proceeded based on the mark, without re-confirming with the patient or family. Post-operatively, the patient awoke to discover the healthy right knee had been replaced, requiring a second, corrective surgery on the left knee and prolonged rehabilitation, significantly impacting his quality of life and leading to permanent disability in the unnecessarily operated limb. The hospital's contingency plan for EMR downtime was incomplete, leading to fragmented information flow and reliance on less reliable methods.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>**Surgery**</t>
+          <t>**Radiology/Imaging**</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>During a complex five-hour spinal fusion procedure, the surgical team was experiencing significant delays due to unexpected anatomical challenges and a demanding surgeon who was audibly pushing to expedite the closure. Towards the end of the procedure, a sponge count was initiated, which initially revealed one surgical sponge unaccounted for. The scrub nurse and circulating nurse searched the operative field and surrounding drapes quickly but, under intense pressure and verbal cues from the surgeon who stated it was likely "off the field" or discarded, they eventually falsely reconciled the count as correct to avoid further delays. Post-operatively, the patient developed increasing, unexplained back pain and a persistent low-grade fever. Imaging performed a week later confirmed the presence of a retained surgical sponge. This necessitated a second invasive surgery to remove the foreign object, significantly prolonging the patient's recovery, increasing their hospital stay, and exposing them to additional risks of infection and anesthesia. The hospital's culture of expedience, coupled with a lack of a standardized, robust "timeout" procedure specifically for count reconciliation that empowered nursing staff to halt closure, contributed to this serious outcome.</t>
+          <t>A 55-year-old patient with a known shellfish allergy was scheduled for a CT scan with contrast to evaluate abdominal pain. The radiology technologist, rushing due to a backlog of patients and understaffing, quickly reviewed the electronic order but missed the prominent allergy alert flagged in the patient's chart history, which required a specific pre-medication protocol. The patient received the standard iodine-based contrast agent intravenously. Within minutes, the patient developed a severe urticarial rash and mild respiratory distress. The rapid response team was called, and antihistamines and steroids were administered, successfully resolving the acute reaction. The patient was monitored for several hours and discharged without lasting sequelae, but the event caused significant distress and delayed diagnostic imaging. The hospital had recently implemented a new EMR system with a less intuitive alert interface, which contributed to the oversight.</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>A 45-year-old patient, Mr. John Smith, arrived at the busy emergency department complaining of severe abdominal pain. At the same time, another patient, Mr. Jonathan Smythe, was due for a follow-up appointment in an adjacent outpatient clinic, also for abdominal issues. A new ER admitting clerk, overwhelmed by the influx of patients and relying on a quick glance at the whiteboard, mistakenly printed Mr. Jonathan Smythe's electronic chart and wristband for Mr. John Smith. The ER triage nurse, accustomed to verifying names and dates of birth, asked "Are you Mr. Smythe?" and the patient, disoriented by pain and the unfamiliar environment, simply nodded. He was then taken to a procedure room and prepped for an urgent paracentesis that was actually intended for Mr. Smythe, who had significant ascites. Just as the physician was about to perform the procedure, the physician's assistant, reviewing the patient's old records on the computer, noticed a significant discrepancy between the patient's appearance and the photos in Mr. Smythe's chart, and also that the current symptoms (acute pain, no ascites) didn't align with the ordered procedure. This timely observation halted the procedure, averting a critical error of performing an invasive procedure on the wrong patient. The hospital's high patient volume, reliance on manual data entry in a chaotic environment, and insufficient multi-step identity verification processes in the ER contributed to this near-miss.</t>
+          <t>In the Emergency Department, a nurse was preparing to administer a high-alert medication, intravenous insulin, to a diabetic patient admitted for hyperglycemia. The electronic medication administration record (eMAR) displayed the correct dosage, but a new, inexperienced resident, having just started their rotation, had verbally instructed the nurse to administer double the prescribed dose during a busy moment. The nurse, following the "five rights" of medication administration and performing a double-check on the eMAR and the patient's blood glucose level, noticed the discrepancy between the verbal order and the documented order. Before preparing the medication, she immediately questioned the resident and confirmed with a supervising physician that the original, lower dose was correct. The potential for a severe hypoglycemic event was averted without any harm to the patient. The ER's fast-paced environment and the resident's inexperience contributed to the near miss.</t>
         </is>
       </c>
     </row>

--- a/src/datapipeline/outputs/medical_incidents.xlsx
+++ b/src/datapipeline/outputs/medical_incidents.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,36 +443,120 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>**Surgery**</t>
+          <t>**Internal Medicine**</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>A 72-year-old male underwent elective knee replacement surgery. During the procedure, the surgical team relied on a hand-written white board for patient information and surgical site verification, as the electronic system was temporarily down. The pre-operative checklist was completed verbally but the consent form in the paper chart was for the left knee, while the patient's intended surgery was for the right knee, as indicated by a faint marker on the wrong leg. The surgeon proceeded based on the mark, without re-confirming with the patient or family. Post-operatively, the patient awoke to discover the healthy right knee had been replaced, requiring a second, corrective surgery on the left knee and prolonged rehabilitation, significantly impacting his quality of life and leading to permanent disability in the unnecessarily operated limb. The hospital's contingency plan for EMR downtime was incomplete, leading to fragmented information flow and reliance on less reliable methods.</t>
+          <t>An elderly patient admitted for community-acquired pneumonia developed severe C. difficile infection during their stay, leading to septic shock and prolonged ICU admission. The hospital's infection control audits consistently showed low compliance with enhanced contact precautions, particularly hand hygiene, on the medical ward. The nursing staff reported feeling overwhelmed by high patient-to-nurse ratios, which often led to rushed care and shortcuts in protocol, despite repeated educational modules on C. difficile prevention. The patient's family later attributed his significant decline and extended recovery to this preventable hospital-acquired infection.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>**Radiology/Imaging**</t>
+          <t>**Surgery**</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>A 55-year-old patient with a known shellfish allergy was scheduled for a CT scan with contrast to evaluate abdominal pain. The radiology technologist, rushing due to a backlog of patients and understaffing, quickly reviewed the electronic order but missed the prominent allergy alert flagged in the patient's chart history, which required a specific pre-medication protocol. The patient received the standard iodine-based contrast agent intravenously. Within minutes, the patient developed a severe urticarial rash and mild respiratory distress. The rapid response team was called, and antihistamines and steroids were administered, successfully resolving the acute reaction. The patient was monitored for several hours and discharged without lasting sequelae, but the event caused significant distress and delayed diagnostic imaging. The hospital had recently implemented a new EMR system with a less intuitive alert interface, which contributed to the oversight.</t>
+          <t>During an elective laparoscopic appendectomy, the surgeon encountered atypical anatomy and struggled to identify the appendix correctly. Despite this, the procedure continued without the use of a time-out for a second opinion or intraoperative imaging, which were available options. The hospital had a culture where junior surgeons were hesitant to call for senior assistance unless absolutely necessary, fearing judgment. The surgeon inadvertently perforated the bowel and damaged adjacent structures, leading to a complex repair, significant postoperative infection, and an extended hospital stay for the patient, requiring a second surgery.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>**Ob/Gyn/NICU**</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>A premature infant in the Neonatal Intensive Care Unit (NICU) was prescribed a low dose of an opioid for pain management post-surgery. During preparation, a new pharmacy technician, who was covering for an absent colleague and unfamiliar with the specific NICU dosing protocols, accidentally prepared a tenfold higher concentration of the medication. The hospital's automated dispensing cabinet had recently been updated, causing some confusion with label formats, and a double-check by a second pharmacist, typically required for high-risk medications, was omitted due to urgent demand elsewhere and understaffing. The error was caught by the NICU nurse, who questioned the volume for the ordered dose, just before administration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>**Radiology/Imaging**</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>A patient with a history of claustrophobia was scheduled for an MRI. Despite being premedicated with an anxiolytic, the patient became extremely agitated in the scanner, requiring the procedure to be aborted mid-scan. The hospital’s standard pre-MRI screening questionnaire did not adequately assess the severity of claustrophobia or prior negative experiences, relying solely on a simple "yes/no" question. The radiology department was under pressure to minimize scan times, leading technologists to proceed quickly without exploring patient anxiety levels in detail, resulting in wasted resources and a rescheduled, longer visit for the patient.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>**Outpatient/ER**</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>In the Emergency Department, a nurse was preparing to administer a high-alert medication, intravenous insulin, to a diabetic patient admitted for hyperglycemia. The electronic medication administration record (eMAR) displayed the correct dosage, but a new, inexperienced resident, having just started their rotation, had verbally instructed the nurse to administer double the prescribed dose during a busy moment. The nurse, following the "five rights" of medication administration and performing a double-check on the eMAR and the patient's blood glucose level, noticed the discrepancy between the verbal order and the documented order. Before preparing the medication, she immediately questioned the resident and confirmed with a supervising physician that the original, lower dose was correct. The potential for a severe hypoglycemic event was averted without any harm to the patient. The ER's fast-paced environment and the resident's inexperience contributed to the near miss.</t>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>A patient presented to the Emergency Room with worsening abdominal pain, nausea, and vomiting over 48 hours. After initial evaluation, the ER physician, attributing the symptoms to gastroenteritis, discharged the patient with anti-emetics and advice to follow up with their primary care doctor. The hospital’s ER was experiencing extreme overcrowding, leading to an average patient-to-physician ratio that made thorough reassessment difficult. No abdominal imaging was ordered despite the increasing severity of pain, as the department had a policy to conserve resources during peak hours. The patient returned 12 hours later via ambulance with a ruptured appendix, requiring emergency surgery and a prolonged recovery from peritonitis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>**Internal Medicine**</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>A patient with diabetes on a medical ward received their morning insulin dose. Later in the morning, a different nurse, mistakenly believing the patient had not yet received their dose (due to an incomplete charting entry from the first nurse who was pulled to an emergency), prepared and administered a second, identical dose. The hospital's new electronic charting system was prone to intermittent network delays, causing entries to appear incomplete temporarily, and a recent update had changed the workflow for medication administration verification without adequate staff training. The patient experienced a hypoglycemic episode, which was quickly recognized and treated without lasting harm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>**Surgery**</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>During a knee arthroscopy, the surgical team was using a new, minimally invasive device. Before the procedure began, the scrub nurse noted that one of the single-use components of the device packaging appeared slightly compromised, but dismissed it as minor manufacturing defect. The hospital's procurement department had recently switched suppliers for this device to save costs, and staff had expressed concerns about the quality of packaging. The procedure proceeded, and post-operatively, the patient developed a deep joint infection requiring intravenous antibiotics and further surgical washout, likely stemming from a breach in sterility related to the compromised packaging.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>**Ob/Gyn/NICU**</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>A new mother in the postpartum unit was struggling with breastfeeding her jaundiced infant. Despite multiple calls from the mother expressing concern about the baby's poor feeding and lethargy, the nursing staff, facing a high patient census, reassured her that "all new mothers struggle" and focused on promoting breastfeeding without further assessment. The hospital had recently cut lactation consultant hours to reduce costs. By day three, the infant became severely dehydrated and required readmission to the NICU for intravenous fluids and phototherapy, primarily due to insufficient milk intake, which could have been identified earlier with more thorough assessment and support.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>**Radiology/Imaging**</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>A technologist was preparing a patient for a chest X-ray. Due to a momentary distraction from an urgent phone call about another patient, they incorrectly positioned the X-ray tube. The resulting image was technically diagnostic, but the field of view was slightly off-center, missing a small portion of one lung apex. The hospital's protocol required a full re-take for any positioning error, but the technologist, under pressure to meet departmental throughput targets, decided against it. The error was caught by the interpreting radiologist, who requested a repeat X-ray, leading to a minor delay for the patient and a minor increase in radiation exposure, but no missed diagnosis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>**Outpatient/ER**</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>An elderly patient with a history of severe sulfa allergy presented to an outpatient clinic for a urinary tract infection. The physician, using the electronic health record (EHR) system, prescribed a sulfa-containing antibiotic. While the allergy was clearly documented in the patient's chart, the EHR's alert system for drug-allergy interactions was experiencing a known software glitch that day, preventing it from firing critical warnings. The prescription was transmitted to the pharmacy without an alert. Fortunately, the outpatient pharmacy's manual verification process caught the contraindication before the medication was dispensed to the patient, averting a potentially severe allergic reaction.</t>
         </is>
       </c>
     </row>
